--- a/starter-kit/出力例/手順書サンプル.xlsx
+++ b/starter-kit/出力例/手順書サンプル.xlsx
@@ -59,7 +59,7 @@
     <t>共有フォルダの場所（\\ から始まる文字列）が手元に控えてあること。</t>
   </si>
   <si>
-    <t>2-2</t>
+    <t>2-1</t>
   </si>
   <si>
     <t xml:space="preserve">ネットワークドライブの割り当て
@@ -75,7 +75,7 @@
     <t>黒い画面（コマンドプロンプト）が開くこと。</t>
   </si>
   <si>
-    <t>2-3</t>
+    <t>2-2</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -89,7 +89,7 @@
     <t>「コマンドは正常に終了しました。」と表示されること。</t>
   </si>
   <si>
-    <t>2-4</t>
+    <t>2-3</t>
   </si>
   <si>
     <t xml:space="preserve">エクスプローラーで確認する
@@ -100,7 +100,7 @@
     <t>共有フォルダの中身が表示されること。</t>
   </si>
   <si>
-    <t>2-5</t>
+    <t>2-4</t>
   </si>
   <si>
     <t xml:space="preserve">後片付け

--- a/starter-kit/出力例/手順書サンプル.xlsx
+++ b/starter-kit/出力例/手順書サンプル.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="28">
   <si>
     <t>共有フォルダをネットワークドライブに割り当てる手順</t>
   </si>
@@ -47,8 +47,7 @@
   </si>
   <si>
     <t xml:space="preserve">準備
-1. 管理者から届いたメールを開きます。
-2. メールに書かれている共有フォルダの場所（例: \\fileserver\share）を控えます。 </t>
+ </t>
   </si>
   <si>
     <t xml:space="preserve">共有フォルダの場所を確認する
@@ -56,6 +55,10 @@
 2. メールに書かれている共有フォルダの場所（例: \\fileserver\share）を控えます。</t>
   </si>
   <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
     <t>共有フォルダの場所（\\ から始まる文字列）が手元に控えてあること。</t>
   </si>
   <si>
@@ -63,8 +66,7 @@
   </si>
   <si>
     <t xml:space="preserve">ネットワークドライブの割り当て
-1. キーボードの Windows キー を押します。
-2. cmd と入力し、コマンド プロンプト をクリックします。 </t>
+ </t>
   </si>
   <si>
     <t xml:space="preserve">コマンドプロンプトを開く
@@ -81,9 +83,39 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">ドライブを割り当てる
-1. 次のコマンドを入力し、Enter キーを押します。net use Z: \\fileserver\share /persistent:yes
+    <r>
+      <rPr>
+        <charset val="1"/>
+        <color theme="1"/>
+        <family val="2"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ドライブを割り当てる
+1. 次のコマンドを入力し、Enter キーを押します。</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="1"/>
+        <color rgb="FFC7254E"/>
+        <family val="2"/>
+        <sz val="11"/>
+        <rFont val="Consolas"/>
+      </rPr>
+      <t xml:space="preserve">net use Z: \\fileserver\share /persistent:yes
+</t>
+    </r>
+    <r>
+      <rPr>
+        <charset val="1"/>
+        <color theme="1"/>
+        <family val="2"/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">
 2. ユーザー名とパスワードを聞かれた場合は、社内アカウントの情報を入力します。</t>
+    </r>
   </si>
   <si>
     <t>「コマンドは正常に終了しました。」と表示されること。</t>
@@ -258,16 +290,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>428625</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>3838575</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1781175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -625,19 +657,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="15.94" customWidth="1"/>
     <col min="3" max="3" width="50.08" customWidth="1"/>
     <col min="4" max="4" width="79.18" customWidth="1"/>
-    <col min="5" max="5" width="59.24" customWidth="1"/>
-    <col min="6" max="6" width="9.1" customWidth="1"/>
-    <col min="7" max="7" width="12.74" customWidth="1"/>
-    <col min="8" max="8" width="14.56" customWidth="1"/>
+    <col min="5" max="5" width="63.12" customWidth="1"/>
+    <col min="6" max="6" width="59.24" customWidth="1"/>
+    <col min="7" max="7" width="9.1" customWidth="1"/>
+    <col min="8" max="8" width="12.74" customWidth="1"/>
+    <col min="9" max="9" width="14.56" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="31.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" ht="31.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -648,8 +681,9 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
-    <row r="2" ht="19.5" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="19.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -660,8 +694,9 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
-    <row r="3" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="4" t="s">
         <v>2</v>
@@ -672,20 +707,21 @@
       <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="34.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" ht="66" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -698,127 +734,142 @@
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6" t="s">
-        <v>9</v>
+      <c r="F4" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I4" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" ht="34.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="66" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="6" t="s">
-        <v>9</v>
+      <c r="E5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>18</v>
       </c>
       <c r="G5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" ht="34.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" ht="115.5" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" ht="146.25" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H6" s="8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I7" s="8" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" ht="34.8" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" ht="36.8" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>9</v>
       </c>
       <c r="G8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="8" t="s">
         <v>9</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="0" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
